--- a/data/lexicon_review/Moroccan.xlsx
+++ b/data/lexicon_review/Moroccan.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
@@ -535,17 +535,17 @@
           <t>ئ</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
         <is>
           <t>ل</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>ة</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -557,7 +557,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>assila</t>
+          <t>as2ila</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -569,25 +569,29 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ss</t>
+          <t>s</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>i</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -624,11 +628,31 @@
         <v>1</v>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>س</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ئ</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ة</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -641,16 +665,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sou2al</t>
+          <t>assila</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ss</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -685,35 +729,15 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>أ</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>س</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ئ</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>ل</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>ة</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -725,41 +749,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>as2ila</t>
+          <t>assela</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -813,7 +813,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>assela</t>
+          <t>sou2al</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -870,12 +870,12 @@
           <t>س</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>ئ</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>ل</t>
@@ -897,7 +897,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ass2ila</t>
+          <t>as ilat</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -909,12 +909,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ss</t>
+          <t>s</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>at</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -978,12 +978,12 @@
           <t>س</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>ئ</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>ل</t>
@@ -1005,7 +1005,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>as ilat</t>
+          <t>ass2ila</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>ss</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t> </t>
+          <t>2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>at</t>
+          <t>a</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -1252,11 +1252,31 @@
         <v>1</v>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>إ</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ن</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>س</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ن</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1269,16 +1289,36 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bnadm</t>
+          <t>2nsan</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1313,7 +1353,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
@@ -1353,14 +1393,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2nsan</t>
+          <t>insan</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>i</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1417,34 +1457,14 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>إ</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>ن</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>س</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>ن</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -1457,36 +1477,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>insan</t>
+          <t>bnadm</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
@@ -1561,7 +1561,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>insane</t>
+          <t>inssan</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>ss</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1591,11 +1591,7 @@
           <t>n</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -1629,7 +1625,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
@@ -1669,7 +1665,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>inssan</t>
+          <t>insane</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1686,7 +1682,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ss</t>
+          <t>s</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1699,7 +1695,11 @@
           <t>n</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
@@ -1908,21 +1908,9 @@
         <v>1</v>
       </c>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>آ</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>خ</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>ر</t>
-        </is>
-      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -1937,26 +1925,14 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>akhr</t>
+          <t>lkhr</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>kh</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -2013,7 +1989,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>lkhr</t>
+          <t>tali</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2060,9 +2036,21 @@
         <v>1</v>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>آ</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>خ</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ر</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -2077,14 +2065,26 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>tali</t>
+          <t>akhr</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>kh</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
@@ -2153,7 +2153,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>akhir</t>
+          <t>akhor</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>o</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
@@ -2245,7 +2245,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>akhor</t>
+          <t>akhir</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>i</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2557,7 +2557,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
@@ -2589,7 +2589,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>joz2</t>
+          <t>jaza</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2609,12 +2609,12 @@
           <t>z</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -2649,13 +2649,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ج</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>ز</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>ء</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
@@ -2669,15 +2681,31 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>part</t>
+          <t>joz2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>j</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>z</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
@@ -2780,22 +2808,10 @@
         <v>1</v>
       </c>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>ج</t>
-        </is>
-      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>ز</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>ء</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
@@ -2809,32 +2825,16 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>jaza</t>
+          <t>part</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>j</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>z</t>
-        </is>
-      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
@@ -3128,11 +3128,23 @@
         <v>1</v>
       </c>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ج</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>ز</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>ء</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
@@ -3145,19 +3157,47 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve"> chiwya</t>
+          <t>jouzeae</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>j</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>z</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
@@ -3192,23 +3232,11 @@
         <v>1</v>
       </c>
       <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>ج</t>
-        </is>
-      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>ز</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>ء</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -3221,47 +3249,19 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>jouzeae</t>
+          <t xml:space="preserve"> chiwya</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>j</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>o</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>z</t>
-        </is>
-      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
@@ -3365,22 +3365,22 @@
           <t>ر</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
         <is>
           <t>ئ</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>ي</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>س</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -3393,7 +3393,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>raiss</t>
+          <t>ra2is</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -3410,15 +3410,19 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
           <t>i</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>ss</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
@@ -3453,7 +3457,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
@@ -3461,22 +3465,22 @@
           <t>ر</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>ئ</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>ئ</t>
+          <t>ي</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>ي</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
           <t>س</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
@@ -3489,7 +3493,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ra2is</t>
+          <t>raiss</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -3506,19 +3510,15 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>i</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+          <t>ss</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
@@ -3589,7 +3589,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ra-iss</t>
+          <t>ra2iss</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
@@ -3689,7 +3689,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ra2iss</t>
+          <t>ra-iss</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
@@ -3871,12 +3871,12 @@
           <t>ا</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
         <is>
           <t>ل</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
@@ -3889,7 +3889,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>soual</t>
+          <t>so2al</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -3901,20 +3901,24 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ou</t>
+          <t>o</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
           <t>a</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
@@ -3949,7 +3953,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
@@ -3967,12 +3971,12 @@
           <t>ا</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t>ل</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
@@ -3985,7 +3989,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>so2al</t>
+          <t>soual</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -3997,24 +4001,20 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>ou</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
           <t>l</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
@@ -4157,23 +4157,23 @@
           <t>س</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
         <is>
           <t>ؤ</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="H125" t="inlineStr">
         <is>
           <t>ا</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr">
+      <c r="I125" t="inlineStr">
         <is>
           <t>ل</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
@@ -4185,7 +4185,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>sou2al</t>
+          <t>sou-al</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -4197,25 +4197,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>ou</t>
+          <t>o</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>u</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
           <t>a</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
+      <c r="I126" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
@@ -4249,7 +4253,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
@@ -4257,23 +4261,23 @@
           <t>س</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
+      <c r="E128" t="inlineStr">
         <is>
           <t>ؤ</t>
         </is>
       </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
           <t>ل</t>
         </is>
       </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
@@ -4285,7 +4289,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>sou-al</t>
+          <t>sou2al</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -4297,29 +4301,25 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>ou</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
           <t>l</t>
         </is>
       </c>
+      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
@@ -4417,17 +4417,45 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>س</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>ت</t>
+        </is>
+      </c>
       <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>ع</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
@@ -4437,19 +4465,47 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>استعمال</t>
+          <t>sti3mal</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
@@ -4481,45 +4537,17 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>س</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>ت</t>
-        </is>
-      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>ع</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>م</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>ل</t>
-        </is>
-      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
@@ -4529,47 +4557,19 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>sti3mal</t>
+          <t>استعمال</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
@@ -4713,14 +4713,14 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>isti3mal</t>
+          <t>asta3mal</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
@@ -4837,14 +4837,14 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>asta3mal</t>
+          <t>isti3mal</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>i</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>i</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -4916,16 +4916,44 @@
         <v>1</v>
       </c>
       <c r="C149" t="inlineStr"/>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>س</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>ت</t>
+        </is>
+      </c>
       <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>ع</t>
+        </is>
+      </c>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr"/>
@@ -4933,21 +4961,61 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>it depends</t>
+          <t>istiaeamal</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr"/>
@@ -4980,44 +5048,16 @@
         <v>1</v>
       </c>
       <c r="C152" t="inlineStr"/>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>س</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>ت</t>
-        </is>
-      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>ع</t>
-        </is>
-      </c>
+      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>م</t>
-        </is>
-      </c>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>ل</t>
-        </is>
-      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr"/>
@@ -5025,61 +5065,21 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>istiaeamal</t>
+          <t>it depends</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr"/>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr"/>
@@ -5173,49 +5173,17 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>س</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>ت</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>ع</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>م</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>ل</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>و</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
@@ -5225,42 +5193,18 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>st3mlo</t>
+          <t>khedmu</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>o</t>
-        </is>
-      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr"/>
@@ -5293,17 +5237,49 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C161" t="inlineStr"/>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>س</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>ت</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>ع</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>و</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
@@ -5313,18 +5289,42 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>khedmu</t>
+          <t>st3mlo</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr"/>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
@@ -5375,32 +5375,32 @@
           <t>ت</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
         <is>
           <t>ع</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
+      <c r="I164" t="inlineStr">
         <is>
           <t>م</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
+      <c r="J164" t="inlineStr">
         <is>
           <t>ل</t>
         </is>
       </c>
-      <c r="J164" t="inlineStr">
+      <c r="K164" t="inlineStr">
         <is>
           <t>و</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
+      <c r="L164" t="inlineStr">
         <is>
           <t>ا</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
@@ -5409,7 +5409,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>st3mlou</t>
+          <t>sta3mlo</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -5427,25 +5427,29 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
+      <c r="I165" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
+      <c r="J165" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>ou</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr"/>
       <c r="N165" t="inlineStr"/>
@@ -5601,7 +5605,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
@@ -5619,32 +5623,32 @@
           <t>ت</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>ع</t>
+        </is>
+      </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>ع</t>
+          <t>م</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>م</t>
+          <t>ل</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>ل</t>
+          <t>و</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>و</t>
-        </is>
-      </c>
-      <c r="L170" t="inlineStr">
-        <is>
           <t>ا</t>
         </is>
       </c>
+      <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr"/>
@@ -5653,7 +5657,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>sta3mlo</t>
+          <t>st3mlou</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -5671,29 +5675,25 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>m</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>l</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>o</t>
-        </is>
-      </c>
+          <t>ou</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
@@ -5725,7 +5725,7 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
@@ -5777,7 +5777,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>sta3mlou</t>
+          <t>ste3mlou</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
@@ -5901,12 +5901,16 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ste3mlou</t>
+          <t>ista3mlo</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr"/>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>s</t>
@@ -5919,7 +5923,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -5939,7 +5943,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>ou</t>
+          <t>o</t>
         </is>
       </c>
       <c r="L177" t="inlineStr"/>
@@ -6025,16 +6029,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ista3mlo</t>
+          <t>sta3mlou</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr"/>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
           <t>s</t>
@@ -6067,7 +6067,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>ou</t>
         </is>
       </c>
       <c r="L180" t="inlineStr"/>
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
@@ -6326,22 +6326,22 @@
           <t>م</t>
         </is>
       </c>
-      <c r="J188" t="inlineStr">
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
         <is>
           <t>ل</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
+      <c r="L188" t="inlineStr">
         <is>
           <t>و</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr">
+      <c r="M188" t="inlineStr">
         <is>
           <t>ا</t>
         </is>
       </c>
-      <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr"/>
@@ -6349,54 +6349,54 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>asta3mloua</t>
+          <t>ista3malou</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
+      <c r="K189" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
+      <c r="L189" t="inlineStr">
         <is>
           <t>ou</t>
-        </is>
-      </c>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t>a</t>
         </is>
       </c>
       <c r="M189" t="inlineStr"/>
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
@@ -6458,22 +6458,22 @@
           <t>م</t>
         </is>
       </c>
-      <c r="J191" t="inlineStr"/>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>ل</t>
+          <t>و</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>و</t>
-        </is>
-      </c>
-      <c r="M191" t="inlineStr">
-        <is>
           <t>ا</t>
         </is>
       </c>
+      <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr"/>
@@ -6481,14 +6481,14 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ista3malou</t>
+          <t>asta3mloua</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -6518,17 +6518,17 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>ou</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
           <t>a</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="L192" t="inlineStr">
-        <is>
-          <t>ou</t>
         </is>
       </c>
       <c r="M192" t="inlineStr"/>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
@@ -6897,32 +6897,32 @@
           <t>ت</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>ل</t>
+          <t>ف</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>ف</t>
+          <t>ا</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
+          <t>ز</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
           <t>ا</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>ز</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
+      <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr"/>
@@ -6933,7 +6933,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>tilvaz</t>
+          <t>tlfaza</t>
         </is>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -6945,27 +6945,27 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>l</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>f</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>v</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
+          <t>z</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
           <t>a</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>z</t>
         </is>
       </c>
       <c r="J207" t="inlineStr"/>
@@ -7009,32 +7009,32 @@
           <t>ت</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr">
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
         <is>
           <t>ل</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
+      <c r="G209" t="inlineStr">
         <is>
           <t>ف</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
+      <c r="H209" t="inlineStr">
         <is>
           <t>ا</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
+      <c r="I209" t="inlineStr">
         <is>
           <t>ز</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr">
+      <c r="J209" t="inlineStr">
         <is>
           <t>ا</t>
         </is>
       </c>
-      <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr"/>
@@ -7045,7 +7045,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>tlfasa</t>
+          <t>tilvaz</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -7057,27 +7057,27 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
           <t>l</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
       <c r="G210" t="inlineStr">
         <is>
+          <t>v</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
           <t>a</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>z</t>
         </is>
       </c>
       <c r="J210" t="inlineStr"/>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
@@ -7269,7 +7269,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>tlfaza</t>
+          <t>tlfasa</t>
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>z</t>
+          <t>s</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -8017,7 +8017,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
@@ -8061,7 +8061,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>placar</t>
+          <t>plaqar</t>
         </is>
       </c>
       <c r="B240" t="inlineStr"/>
@@ -8083,7 +8083,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>q</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -8241,7 +8241,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
@@ -8285,7 +8285,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>plaqar</t>
+          <t>placar</t>
         </is>
       </c>
       <c r="B246" t="inlineStr"/>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>q</t>
+          <t>c</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -8597,7 +8597,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr">
@@ -8633,7 +8633,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>mital</t>
+          <t>matal</t>
         </is>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -8697,7 +8697,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
@@ -8733,7 +8733,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>matal</t>
+          <t>mital</t>
         </is>
       </c>
       <c r="B261" t="inlineStr"/>
@@ -8745,7 +8745,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>i</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -9493,7 +9493,7 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
@@ -9529,7 +9529,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>cherjem</t>
+          <t>charjam</t>
         </is>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -9556,7 +9556,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
@@ -9633,7 +9633,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>charjam</t>
+          <t>cherjem</t>
         </is>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -9645,7 +9645,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -9660,7 +9660,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -10297,7 +10297,7 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
@@ -10333,14 +10333,14 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>7ammam</t>
+          <t>hammam</t>
         </is>
       </c>
       <c r="B312" t="inlineStr"/>
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>h</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -10397,7 +10397,7 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
@@ -10433,14 +10433,14 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>hammam</t>
+          <t>7ammam</t>
         </is>
       </c>
       <c r="B315" t="inlineStr"/>
       <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -10661,7 +10661,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>sbah</t>
+          <t>sba7</t>
         </is>
       </c>
       <c r="B324" t="inlineStr"/>
@@ -10683,7 +10683,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H324" t="inlineStr"/>
@@ -10757,7 +10757,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>sba7</t>
+          <t>sbah</t>
         </is>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>h</t>
         </is>
       </c>
       <c r="H327" t="inlineStr"/>
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
@@ -10825,22 +10825,22 @@
           <t>ص</t>
         </is>
       </c>
-      <c r="E329" t="inlineStr">
+      <c r="E329" t="inlineStr"/>
+      <c r="F329" t="inlineStr">
         <is>
           <t>ب</t>
         </is>
       </c>
-      <c r="F329" t="inlineStr">
+      <c r="G329" t="inlineStr">
         <is>
           <t>ا</t>
         </is>
       </c>
-      <c r="G329" t="inlineStr">
+      <c r="H329" t="inlineStr">
         <is>
           <t>ح</t>
         </is>
       </c>
-      <c r="H329" t="inlineStr"/>
       <c r="I329" t="inlineStr"/>
       <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr"/>
@@ -10853,7 +10853,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t xml:space="preserve">sbah </t>
+          <t>saba7</t>
         </is>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -10865,20 +10865,24 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
           <t>b</t>
         </is>
       </c>
-      <c r="F330" t="inlineStr">
+      <c r="G330" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="H330" t="inlineStr"/>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="I330" t="inlineStr"/>
       <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr"/>
@@ -10913,7 +10917,7 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
@@ -10921,22 +10925,22 @@
           <t>ص</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>ب</t>
+          <t>ا</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="H332" t="inlineStr">
-        <is>
           <t>ح</t>
         </is>
       </c>
+      <c r="H332" t="inlineStr"/>
       <c r="I332" t="inlineStr"/>
       <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr"/>
@@ -10949,7 +10953,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>saba7</t>
+          <t xml:space="preserve">sbah </t>
         </is>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -10961,24 +10965,20 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr"/>
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr"/>
@@ -11537,7 +11537,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t xml:space="preserve">skhun </t>
+          <t xml:space="preserve"> skhon</t>
         </is>
       </c>
       <c r="B354" t="inlineStr"/>
@@ -11554,7 +11554,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>o</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
@@ -11597,7 +11597,7 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
@@ -11633,7 +11633,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>skhoun</t>
+          <t xml:space="preserve">skhun </t>
         </is>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>ou</t>
+          <t>u</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
@@ -11693,7 +11693,7 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
@@ -11729,7 +11729,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t xml:space="preserve"> skhon</t>
+          <t>skhoun</t>
         </is>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -11746,7 +11746,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>ou</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C383" t="inlineStr"/>
       <c r="D383" t="inlineStr">
@@ -12534,12 +12534,12 @@
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
-      <c r="F383" t="inlineStr"/>
-      <c r="G383" t="inlineStr">
+      <c r="F383" t="inlineStr">
         <is>
           <t>ش</t>
         </is>
       </c>
+      <c r="G383" t="inlineStr"/>
       <c r="H383" t="inlineStr">
         <is>
           <t>ك</t>
@@ -12565,7 +12565,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>mouchkila</t>
+          <t xml:space="preserve">machakil </t>
         </is>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -12577,17 +12577,17 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>ch</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>ch</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -12605,11 +12605,7 @@
           <t>l</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="K384" t="inlineStr"/>
       <c r="L384" t="inlineStr"/>
       <c r="M384" t="inlineStr"/>
       <c r="N384" t="inlineStr"/>
@@ -12641,7 +12637,7 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C386" t="inlineStr"/>
       <c r="D386" t="inlineStr">
@@ -12650,12 +12646,12 @@
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
-      <c r="F386" t="inlineStr">
+      <c r="F386" t="inlineStr"/>
+      <c r="G386" t="inlineStr">
         <is>
           <t>ش</t>
         </is>
       </c>
-      <c r="G386" t="inlineStr"/>
       <c r="H386" t="inlineStr">
         <is>
           <t>ك</t>
@@ -12681,7 +12677,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t xml:space="preserve">machakil </t>
+          <t>mouchkila</t>
         </is>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -12693,35 +12689,39 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F387" t="inlineStr">
-        <is>
-          <t>ch</t>
-        </is>
-      </c>
-      <c r="G387" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="H387" t="inlineStr">
-        <is>
-          <t>k</t>
-        </is>
-      </c>
-      <c r="I387" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="J387" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="K387" t="inlineStr"/>
       <c r="L387" t="inlineStr"/>
       <c r="M387" t="inlineStr"/>
       <c r="N387" t="inlineStr"/>
@@ -12882,12 +12882,12 @@
           <t>ل</t>
         </is>
       </c>
-      <c r="F392" t="inlineStr">
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="inlineStr">
         <is>
           <t>ص</t>
         </is>
       </c>
-      <c r="G392" t="inlineStr"/>
       <c r="H392" t="inlineStr"/>
       <c r="I392" t="inlineStr"/>
       <c r="J392" t="inlineStr"/>
@@ -12901,7 +12901,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>khlss</t>
+          <t>khles</t>
         </is>
       </c>
       <c r="B393" t="inlineStr"/>
@@ -12918,10 +12918,14 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>ss</t>
-        </is>
-      </c>
-      <c r="G393" t="inlineStr"/>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="H393" t="inlineStr"/>
       <c r="I393" t="inlineStr"/>
       <c r="J393" t="inlineStr"/>
@@ -12989,7 +12993,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>khles</t>
+          <t>khlas</t>
         </is>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -13006,7 +13010,7 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
@@ -13062,12 +13066,12 @@
           <t>ل</t>
         </is>
       </c>
-      <c r="F398" t="inlineStr"/>
-      <c r="G398" t="inlineStr">
+      <c r="F398" t="inlineStr">
         <is>
           <t>ص</t>
         </is>
       </c>
+      <c r="G398" t="inlineStr"/>
       <c r="H398" t="inlineStr"/>
       <c r="I398" t="inlineStr"/>
       <c r="J398" t="inlineStr"/>
@@ -13081,7 +13085,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>khlas</t>
+          <t>khlss</t>
         </is>
       </c>
       <c r="B399" t="inlineStr"/>
@@ -13098,14 +13102,10 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G399" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+          <t>ss</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr"/>
       <c r="H399" t="inlineStr"/>
       <c r="I399" t="inlineStr"/>
       <c r="J399" t="inlineStr"/>
@@ -13325,7 +13325,7 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr">
@@ -13357,7 +13357,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>khalass</t>
+          <t>kheless</t>
         </is>
       </c>
       <c r="B408" t="inlineStr"/>
@@ -13369,7 +13369,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -13421,7 +13421,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
@@ -13453,7 +13453,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>khelles</t>
+          <t>khalles</t>
         </is>
       </c>
       <c r="B411" t="inlineStr"/>
@@ -13465,7 +13465,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
@@ -13517,7 +13517,7 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
@@ -13549,7 +13549,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>khalles</t>
+          <t>khelles</t>
         </is>
       </c>
       <c r="B414" t="inlineStr"/>
@@ -13561,7 +13561,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
@@ -13613,7 +13613,7 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr">
@@ -13645,7 +13645,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>kheless</t>
+          <t>khalass</t>
         </is>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -13657,7 +13657,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -13667,7 +13667,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -13741,7 +13741,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>khalless</t>
+          <t>khallass</t>
         </is>
       </c>
       <c r="B420" t="inlineStr"/>
@@ -13763,7 +13763,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -13805,7 +13805,7 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr">
@@ -13837,7 +13837,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>khelless</t>
+          <t>khellass</t>
         </is>
       </c>
       <c r="B423" t="inlineStr"/>
@@ -13859,7 +13859,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -13901,7 +13901,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C425" t="inlineStr"/>
       <c r="D425" t="inlineStr">
@@ -13933,7 +13933,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>khellass</t>
+          <t>khelless</t>
         </is>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -13955,7 +13955,7 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -14029,7 +14029,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>khallass</t>
+          <t>khalless</t>
         </is>
       </c>
       <c r="B429" t="inlineStr"/>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -14629,7 +14629,7 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr">
@@ -14669,7 +14669,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>tiara</t>
+          <t>tyara</t>
         </is>
       </c>
       <c r="B450" t="inlineStr"/>
@@ -14681,7 +14681,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>y</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
@@ -14733,7 +14733,7 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
@@ -14773,7 +14773,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>tyara</t>
+          <t>tiara</t>
         </is>
       </c>
       <c r="B453" t="inlineStr"/>
@@ -14785,7 +14785,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
@@ -14837,7 +14837,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr">
@@ -14877,7 +14877,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>tiyara</t>
+          <t>teyara</t>
         </is>
       </c>
       <c r="B456" t="inlineStr"/>
@@ -14889,7 +14889,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr">
@@ -15089,7 +15089,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>teyara</t>
+          <t>tiyara</t>
         </is>
       </c>
       <c r="B462" t="inlineStr"/>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>i</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
@@ -15273,12 +15273,12 @@
           <t>ط</t>
         </is>
       </c>
-      <c r="E467" t="inlineStr">
+      <c r="E467" t="inlineStr"/>
+      <c r="F467" t="inlineStr">
         <is>
           <t>ي</t>
         </is>
       </c>
-      <c r="F467" t="inlineStr"/>
       <c r="G467" t="inlineStr">
         <is>
           <t>ا</t>
@@ -15305,7 +15305,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t xml:space="preserve"> tayara</t>
+          <t>teyyara</t>
         </is>
       </c>
       <c r="B468" t="inlineStr"/>
@@ -15317,12 +15317,12 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>yy</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
@@ -15381,12 +15381,12 @@
           <t>ط</t>
         </is>
       </c>
-      <c r="E470" t="inlineStr"/>
-      <c r="F470" t="inlineStr">
+      <c r="E470" t="inlineStr">
         <is>
           <t>ي</t>
         </is>
       </c>
+      <c r="F470" t="inlineStr"/>
       <c r="G470" t="inlineStr">
         <is>
           <t>ا</t>
@@ -15413,7 +15413,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>teyyara</t>
+          <t xml:space="preserve"> tayara</t>
         </is>
       </c>
       <c r="B471" t="inlineStr"/>
@@ -15425,12 +15425,12 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>yy</t>
+          <t>y</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
@@ -15481,7 +15481,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr">
@@ -15489,12 +15489,12 @@
           <t>ط</t>
         </is>
       </c>
-      <c r="E473" t="inlineStr"/>
-      <c r="F473" t="inlineStr">
+      <c r="E473" t="inlineStr">
         <is>
           <t>ي</t>
         </is>
       </c>
+      <c r="F473" t="inlineStr"/>
       <c r="G473" t="inlineStr">
         <is>
           <t>ا</t>
@@ -15521,7 +15521,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>tayyara</t>
+          <t xml:space="preserve">teyara </t>
         </is>
       </c>
       <c r="B474" t="inlineStr"/>
@@ -15533,12 +15533,12 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>yy</t>
+          <t>y</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
@@ -15589,7 +15589,7 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr">
@@ -15597,12 +15597,12 @@
           <t>ط</t>
         </is>
       </c>
-      <c r="E476" t="inlineStr">
+      <c r="E476" t="inlineStr"/>
+      <c r="F476" t="inlineStr">
         <is>
           <t>ي</t>
         </is>
       </c>
-      <c r="F476" t="inlineStr"/>
       <c r="G476" t="inlineStr">
         <is>
           <t>ا</t>
@@ -15629,7 +15629,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t xml:space="preserve">teyara </t>
+          <t>tayyara</t>
         </is>
       </c>
       <c r="B477" t="inlineStr"/>
@@ -15641,12 +15641,12 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>yy</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
@@ -15729,7 +15729,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>dalm</t>
+          <t>delm</t>
         </is>
       </c>
       <c r="B480" t="inlineStr"/>
@@ -15741,7 +15741,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
@@ -15889,17 +15889,17 @@
           <t>ظ</t>
         </is>
       </c>
-      <c r="E485" t="inlineStr"/>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>ل</t>
-        </is>
-      </c>
-      <c r="G485" t="inlineStr">
-        <is>
           <t>م</t>
         </is>
       </c>
+      <c r="G485" t="inlineStr"/>
       <c r="H485" t="inlineStr"/>
       <c r="I485" t="inlineStr"/>
       <c r="J485" t="inlineStr"/>
@@ -15913,31 +15913,27 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>delm</t>
+          <t>dhlm</t>
         </is>
       </c>
       <c r="B486" t="inlineStr"/>
       <c r="C486" t="inlineStr"/>
       <c r="D486" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>dh</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>l</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="G486" t="inlineStr">
-        <is>
           <t>m</t>
         </is>
       </c>
+      <c r="G486" t="inlineStr"/>
       <c r="H486" t="inlineStr"/>
       <c r="I486" t="inlineStr"/>
       <c r="J486" t="inlineStr"/>
@@ -15981,12 +15977,12 @@
           <t>ظ</t>
         </is>
       </c>
-      <c r="E488" t="inlineStr">
+      <c r="E488" t="inlineStr"/>
+      <c r="F488" t="inlineStr">
         <is>
           <t>ل</t>
         </is>
       </c>
-      <c r="F488" t="inlineStr"/>
       <c r="G488" t="inlineStr">
         <is>
           <t>م</t>
@@ -16005,7 +16001,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>dlam</t>
+          <t>dalm</t>
         </is>
       </c>
       <c r="B489" t="inlineStr"/>
@@ -16017,12 +16013,12 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
           <t>l</t>
-        </is>
-      </c>
-      <c r="F489" t="inlineStr">
-        <is>
-          <t>a</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
@@ -16097,7 +16093,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>dlem</t>
+          <t>dlam</t>
         </is>
       </c>
       <c r="B492" t="inlineStr"/>
@@ -16114,7 +16110,7 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
@@ -16170,12 +16166,12 @@
           <t>ل</t>
         </is>
       </c>
-      <c r="F494" t="inlineStr">
+      <c r="F494" t="inlineStr"/>
+      <c r="G494" t="inlineStr">
         <is>
           <t>م</t>
         </is>
       </c>
-      <c r="G494" t="inlineStr"/>
       <c r="H494" t="inlineStr"/>
       <c r="I494" t="inlineStr"/>
       <c r="J494" t="inlineStr"/>
@@ -16189,14 +16185,14 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>dhlm</t>
+          <t>dlem</t>
         </is>
       </c>
       <c r="B495" t="inlineStr"/>
       <c r="C495" t="inlineStr"/>
       <c r="D495" t="inlineStr">
         <is>
-          <t>dh</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -16206,10 +16202,14 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="G495" t="inlineStr"/>
       <c r="H495" t="inlineStr"/>
       <c r="I495" t="inlineStr"/>
       <c r="J495" t="inlineStr"/>
@@ -16245,7 +16245,7 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr">
@@ -16254,17 +16254,17 @@
         </is>
       </c>
       <c r="E497" t="inlineStr"/>
-      <c r="F497" t="inlineStr">
+      <c r="F497" t="inlineStr"/>
+      <c r="G497" t="inlineStr">
         <is>
           <t>ل</t>
         </is>
       </c>
-      <c r="G497" t="inlineStr">
+      <c r="H497" t="inlineStr">
         <is>
           <t>م</t>
         </is>
       </c>
-      <c r="H497" t="inlineStr"/>
       <c r="I497" t="inlineStr"/>
       <c r="J497" t="inlineStr"/>
       <c r="K497" t="inlineStr"/>
@@ -16277,14 +16277,14 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>ddolm</t>
+          <t>doulm</t>
         </is>
       </c>
       <c r="B498" t="inlineStr"/>
       <c r="C498" t="inlineStr"/>
       <c r="D498" t="inlineStr">
         <is>
-          <t>dd</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -16294,15 +16294,19 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
           <t>l</t>
         </is>
       </c>
-      <c r="G498" t="inlineStr">
+      <c r="H498" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="H498" t="inlineStr"/>
       <c r="I498" t="inlineStr"/>
       <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr"/>
@@ -16429,7 +16433,7 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr">
@@ -16438,17 +16442,17 @@
         </is>
       </c>
       <c r="E503" t="inlineStr"/>
-      <c r="F503" t="inlineStr"/>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>ل</t>
-        </is>
-      </c>
-      <c r="H503" t="inlineStr">
-        <is>
           <t>م</t>
         </is>
       </c>
+      <c r="H503" t="inlineStr"/>
       <c r="I503" t="inlineStr"/>
       <c r="J503" t="inlineStr"/>
       <c r="K503" t="inlineStr"/>
@@ -16461,14 +16465,14 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>doulm</t>
+          <t>ddolm</t>
         </is>
       </c>
       <c r="B504" t="inlineStr"/>
       <c r="C504" t="inlineStr"/>
       <c r="D504" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>dd</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -16478,19 +16482,15 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>l</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="H504" t="inlineStr">
-        <is>
           <t>m</t>
         </is>
       </c>
+      <c r="H504" t="inlineStr"/>
       <c r="I504" t="inlineStr"/>
       <c r="J504" t="inlineStr"/>
       <c r="K504" t="inlineStr"/>
@@ -16589,7 +16589,7 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C509" t="inlineStr"/>
       <c r="D509" t="inlineStr">
@@ -16625,7 +16625,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>ghiam</t>
+          <t>ghyam</t>
         </is>
       </c>
       <c r="B510" t="inlineStr"/>
@@ -16637,7 +16637,7 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>y</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
@@ -16685,7 +16685,7 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C512" t="inlineStr"/>
       <c r="D512" t="inlineStr">
@@ -16721,7 +16721,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>ghyam</t>
+          <t>ghiam</t>
         </is>
       </c>
       <c r="B513" t="inlineStr"/>
@@ -16733,7 +16733,7 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
@@ -16794,18 +16794,18 @@
           <t>ي</t>
         </is>
       </c>
-      <c r="F515" t="inlineStr">
+      <c r="F515" t="inlineStr"/>
+      <c r="G515" t="inlineStr">
         <is>
           <t>ا</t>
         </is>
       </c>
-      <c r="G515" t="inlineStr"/>
-      <c r="H515" t="inlineStr"/>
-      <c r="I515" t="inlineStr">
+      <c r="H515" t="inlineStr">
         <is>
           <t>م</t>
         </is>
       </c>
+      <c r="I515" t="inlineStr"/>
       <c r="J515" t="inlineStr"/>
       <c r="K515" t="inlineStr"/>
       <c r="L515" t="inlineStr"/>
@@ -16817,7 +16817,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>ghyoum</t>
+          <t>ghiyam</t>
         </is>
       </c>
       <c r="B516" t="inlineStr"/>
@@ -16829,25 +16829,25 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
           <t>y</t>
         </is>
       </c>
-      <c r="F516" t="inlineStr"/>
       <c r="G516" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="I516" t="inlineStr">
-        <is>
           <t>m</t>
         </is>
       </c>
+      <c r="I516" t="inlineStr"/>
       <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr"/>
       <c r="L516" t="inlineStr"/>
@@ -16884,27 +16884,11 @@
         <v>1</v>
       </c>
       <c r="C518" t="inlineStr"/>
-      <c r="D518" t="inlineStr">
-        <is>
-          <t>غ</t>
-        </is>
-      </c>
-      <c r="E518" t="inlineStr">
-        <is>
-          <t>ي</t>
-        </is>
-      </c>
+      <c r="D518" t="inlineStr"/>
+      <c r="E518" t="inlineStr"/>
       <c r="F518" t="inlineStr"/>
-      <c r="G518" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="H518" t="inlineStr">
-        <is>
-          <t>م</t>
-        </is>
-      </c>
+      <c r="G518" t="inlineStr"/>
+      <c r="H518" t="inlineStr"/>
       <c r="I518" t="inlineStr"/>
       <c r="J518" t="inlineStr"/>
       <c r="K518" t="inlineStr"/>
@@ -16917,36 +16901,16 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>ghiyam</t>
+          <t>lghyam</t>
         </is>
       </c>
       <c r="B519" t="inlineStr"/>
       <c r="C519" t="inlineStr"/>
-      <c r="D519" t="inlineStr">
-        <is>
-          <t>gh</t>
-        </is>
-      </c>
-      <c r="E519" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="F519" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="G519" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="H519" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+      <c r="D519" t="inlineStr"/>
+      <c r="E519" t="inlineStr"/>
+      <c r="F519" t="inlineStr"/>
+      <c r="G519" t="inlineStr"/>
+      <c r="H519" t="inlineStr"/>
       <c r="I519" t="inlineStr"/>
       <c r="J519" t="inlineStr"/>
       <c r="K519" t="inlineStr"/>
@@ -16984,12 +16948,28 @@
         <v>1</v>
       </c>
       <c r="C521" t="inlineStr"/>
-      <c r="D521" t="inlineStr"/>
-      <c r="E521" t="inlineStr"/>
-      <c r="F521" t="inlineStr"/>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>غ</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>ي</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
       <c r="G521" t="inlineStr"/>
       <c r="H521" t="inlineStr"/>
-      <c r="I521" t="inlineStr"/>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
       <c r="J521" t="inlineStr"/>
       <c r="K521" t="inlineStr"/>
       <c r="L521" t="inlineStr"/>
@@ -17001,17 +16981,37 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>lghyam</t>
+          <t>ghyoum</t>
         </is>
       </c>
       <c r="B522" t="inlineStr"/>
       <c r="C522" t="inlineStr"/>
-      <c r="D522" t="inlineStr"/>
-      <c r="E522" t="inlineStr"/>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>gh</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="F522" t="inlineStr"/>
-      <c r="G522" t="inlineStr"/>
-      <c r="H522" t="inlineStr"/>
-      <c r="I522" t="inlineStr"/>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="J522" t="inlineStr"/>
       <c r="K522" t="inlineStr"/>
       <c r="L522" t="inlineStr"/>
@@ -17141,7 +17141,7 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr">
@@ -17177,7 +17177,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>faran</t>
+          <t>feran</t>
         </is>
       </c>
       <c r="B528" t="inlineStr"/>
@@ -17189,7 +17189,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F528" t="inlineStr">
@@ -17241,7 +17241,7 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr">
@@ -17277,7 +17277,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>feran</t>
+          <t>faran</t>
         </is>
       </c>
       <c r="B531" t="inlineStr"/>
@@ -17289,7 +17289,7 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
@@ -17573,7 +17573,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>farrane</t>
+          <t>ferrane</t>
         </is>
       </c>
       <c r="B540" t="inlineStr"/>
@@ -17585,7 +17585,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F540" t="inlineStr">
@@ -17677,7 +17677,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>ferrane</t>
+          <t>farrane</t>
         </is>
       </c>
       <c r="B543" t="inlineStr"/>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F543" t="inlineStr">
@@ -17745,7 +17745,7 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C545" t="inlineStr"/>
       <c r="D545" t="inlineStr">
@@ -17793,14 +17793,14 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>crafata</t>
+          <t>kravata</t>
         </is>
       </c>
       <c r="B546" t="inlineStr"/>
       <c r="C546" t="inlineStr"/>
       <c r="D546" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>k</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -17815,7 +17815,7 @@
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>v</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C548" t="inlineStr"/>
       <c r="D548" t="inlineStr">
@@ -17913,14 +17913,14 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>cravate</t>
+          <t>gravata</t>
         </is>
       </c>
       <c r="B549" t="inlineStr"/>
       <c r="C549" t="inlineStr"/>
       <c r="D549" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -17950,7 +17950,7 @@
       </c>
       <c r="J549" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="K549" t="inlineStr"/>
@@ -17985,7 +17985,7 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C551" t="inlineStr"/>
       <c r="D551" t="inlineStr">
@@ -18033,14 +18033,14 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>kravata</t>
+          <t>cravata</t>
         </is>
       </c>
       <c r="B552" t="inlineStr"/>
       <c r="C552" t="inlineStr"/>
       <c r="D552" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -18105,7 +18105,7 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C554" t="inlineStr"/>
       <c r="D554" t="inlineStr">
@@ -18153,14 +18153,14 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>cravata</t>
+          <t>grafata</t>
         </is>
       </c>
       <c r="B555" t="inlineStr"/>
       <c r="C555" t="inlineStr"/>
       <c r="D555" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
@@ -18175,7 +18175,7 @@
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>v</t>
+          <t>f</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
@@ -18273,14 +18273,14 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>grafata</t>
+          <t>crafata</t>
         </is>
       </c>
       <c r="B558" t="inlineStr"/>
       <c r="C558" t="inlineStr"/>
       <c r="D558" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
@@ -18345,7 +18345,7 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C560" t="inlineStr"/>
       <c r="D560" t="inlineStr">
@@ -18393,14 +18393,14 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>gravata</t>
+          <t>cravate</t>
         </is>
       </c>
       <c r="B561" t="inlineStr"/>
       <c r="C561" t="inlineStr"/>
       <c r="D561" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
@@ -18430,7 +18430,7 @@
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="K561" t="inlineStr"/>
@@ -19125,7 +19125,7 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C587" t="inlineStr"/>
       <c r="D587" t="inlineStr">
@@ -19157,14 +19157,14 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>gal</t>
+          <t>qal</t>
         </is>
       </c>
       <c r="B588" t="inlineStr"/>
       <c r="C588" t="inlineStr"/>
       <c r="D588" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>q</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
@@ -19213,7 +19213,7 @@
         </is>
       </c>
       <c r="B590" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C590" t="inlineStr"/>
       <c r="D590" t="inlineStr">
@@ -19245,14 +19245,14 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>qal</t>
+          <t>gal</t>
         </is>
       </c>
       <c r="B591" t="inlineStr"/>
       <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr">
         <is>
-          <t>q</t>
+          <t>g</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
@@ -19397,17 +19397,17 @@
           <t>ق</t>
         </is>
       </c>
-      <c r="E596" t="inlineStr"/>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="G596" t="inlineStr">
-        <is>
           <t>ل</t>
         </is>
       </c>
+      <c r="G596" t="inlineStr"/>
       <c r="H596" t="inlineStr"/>
       <c r="I596" t="inlineStr"/>
       <c r="J596" t="inlineStr"/>
@@ -19421,31 +19421,27 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>qual</t>
+          <t xml:space="preserve"> 9al</t>
         </is>
       </c>
       <c r="B597" t="inlineStr"/>
       <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
-          <t>q</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G597" t="inlineStr">
-        <is>
           <t>l</t>
         </is>
       </c>
+      <c r="G597" t="inlineStr"/>
       <c r="H597" t="inlineStr"/>
       <c r="I597" t="inlineStr"/>
       <c r="J597" t="inlineStr"/>
@@ -19513,14 +19509,14 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9al</t>
+          <t>qala</t>
         </is>
       </c>
       <c r="B600" t="inlineStr"/>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>q</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
@@ -19533,7 +19529,11 @@
           <t>l</t>
         </is>
       </c>
-      <c r="G600" t="inlineStr"/>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="H600" t="inlineStr"/>
       <c r="I600" t="inlineStr"/>
       <c r="J600" t="inlineStr"/>
@@ -19660,10 +19660,22 @@
         <v>1</v>
       </c>
       <c r="C605" t="inlineStr"/>
-      <c r="D605" t="inlineStr"/>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>ق</t>
+        </is>
+      </c>
       <c r="E605" t="inlineStr"/>
-      <c r="F605" t="inlineStr"/>
-      <c r="G605" t="inlineStr"/>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
       <c r="H605" t="inlineStr"/>
       <c r="I605" t="inlineStr"/>
       <c r="J605" t="inlineStr"/>
@@ -19677,15 +19689,31 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>galt</t>
+          <t>qual</t>
         </is>
       </c>
       <c r="B606" t="inlineStr"/>
       <c r="C606" t="inlineStr"/>
-      <c r="D606" t="inlineStr"/>
-      <c r="E606" t="inlineStr"/>
-      <c r="F606" t="inlineStr"/>
-      <c r="G606" t="inlineStr"/>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>q</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
       <c r="H606" t="inlineStr"/>
       <c r="I606" t="inlineStr"/>
       <c r="J606" t="inlineStr"/>
@@ -19724,21 +19752,9 @@
         <v>1</v>
       </c>
       <c r="C608" t="inlineStr"/>
-      <c r="D608" t="inlineStr">
-        <is>
-          <t>ق</t>
-        </is>
-      </c>
-      <c r="E608" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="F608" t="inlineStr">
-        <is>
-          <t>ل</t>
-        </is>
-      </c>
+      <c r="D608" t="inlineStr"/>
+      <c r="E608" t="inlineStr"/>
+      <c r="F608" t="inlineStr"/>
       <c r="G608" t="inlineStr"/>
       <c r="H608" t="inlineStr"/>
       <c r="I608" t="inlineStr"/>
@@ -19753,31 +19769,15 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>qala</t>
+          <t>galt</t>
         </is>
       </c>
       <c r="B609" t="inlineStr"/>
       <c r="C609" t="inlineStr"/>
-      <c r="D609" t="inlineStr">
-        <is>
-          <t>q</t>
-        </is>
-      </c>
-      <c r="E609" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F609" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="G609" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="D609" t="inlineStr"/>
+      <c r="E609" t="inlineStr"/>
+      <c r="F609" t="inlineStr"/>
+      <c r="G609" t="inlineStr"/>
       <c r="H609" t="inlineStr"/>
       <c r="I609" t="inlineStr"/>
       <c r="J609" t="inlineStr"/>
@@ -19813,7 +19813,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C611" t="inlineStr"/>
       <c r="D611" t="inlineStr">
@@ -19849,7 +19849,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>bqri</t>
+          <t>bkri</t>
         </is>
       </c>
       <c r="B612" t="inlineStr"/>
@@ -19861,7 +19861,7 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>q</t>
+          <t>k</t>
         </is>
       </c>
       <c r="F612" t="inlineStr">
@@ -19909,7 +19909,7 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr">
@@ -19945,7 +19945,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>bkri</t>
+          <t>bqri</t>
         </is>
       </c>
       <c r="B615" t="inlineStr"/>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>q</t>
         </is>
       </c>
       <c r="F615" t="inlineStr">
@@ -20005,7 +20005,7 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C617" t="inlineStr"/>
       <c r="D617" t="inlineStr">
@@ -20041,7 +20041,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>bekri</t>
+          <t>bakri</t>
         </is>
       </c>
       <c r="B618" t="inlineStr"/>
@@ -20053,7 +20053,7 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F618" t="inlineStr">
@@ -20105,7 +20105,7 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C620" t="inlineStr"/>
       <c r="D620" t="inlineStr">
@@ -20141,7 +20141,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>bakri</t>
+          <t>bekri</t>
         </is>
       </c>
       <c r="B621" t="inlineStr"/>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F621" t="inlineStr">
@@ -20592,13 +20592,33 @@
         <v>1</v>
       </c>
       <c r="C635" t="inlineStr"/>
-      <c r="D635" t="inlineStr"/>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>ك</t>
+        </is>
+      </c>
       <c r="E635" t="inlineStr"/>
-      <c r="F635" t="inlineStr"/>
-      <c r="G635" t="inlineStr"/>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>ر</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>ك</t>
+        </is>
+      </c>
       <c r="H635" t="inlineStr"/>
-      <c r="I635" t="inlineStr"/>
-      <c r="J635" t="inlineStr"/>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>ع</t>
+        </is>
+      </c>
       <c r="K635" t="inlineStr"/>
       <c r="L635" t="inlineStr"/>
       <c r="M635" t="inlineStr"/>
@@ -20609,18 +20629,46 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ge3ga3</t>
+          <t>gurgua3</t>
         </is>
       </c>
       <c r="B636" t="inlineStr"/>
       <c r="C636" t="inlineStr"/>
-      <c r="D636" t="inlineStr"/>
-      <c r="E636" t="inlineStr"/>
-      <c r="F636" t="inlineStr"/>
-      <c r="G636" t="inlineStr"/>
-      <c r="H636" t="inlineStr"/>
-      <c r="I636" t="inlineStr"/>
-      <c r="J636" t="inlineStr"/>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K636" t="inlineStr"/>
       <c r="L636" t="inlineStr"/>
       <c r="M636" t="inlineStr"/>
@@ -20768,33 +20816,13 @@
         <v>1</v>
       </c>
       <c r="C641" t="inlineStr"/>
-      <c r="D641" t="inlineStr">
-        <is>
-          <t>ك</t>
-        </is>
-      </c>
+      <c r="D641" t="inlineStr"/>
       <c r="E641" t="inlineStr"/>
-      <c r="F641" t="inlineStr">
-        <is>
-          <t>ر</t>
-        </is>
-      </c>
-      <c r="G641" t="inlineStr">
-        <is>
-          <t>ك</t>
-        </is>
-      </c>
+      <c r="F641" t="inlineStr"/>
+      <c r="G641" t="inlineStr"/>
       <c r="H641" t="inlineStr"/>
-      <c r="I641" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="J641" t="inlineStr">
-        <is>
-          <t>ع</t>
-        </is>
-      </c>
+      <c r="I641" t="inlineStr"/>
+      <c r="J641" t="inlineStr"/>
       <c r="K641" t="inlineStr"/>
       <c r="L641" t="inlineStr"/>
       <c r="M641" t="inlineStr"/>
@@ -20805,46 +20833,18 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>gurgua3</t>
+          <t xml:space="preserve"> ge3ga3</t>
         </is>
       </c>
       <c r="B642" t="inlineStr"/>
       <c r="C642" t="inlineStr"/>
-      <c r="D642" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="E642" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="F642" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="G642" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="H642" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="I642" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="J642" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="D642" t="inlineStr"/>
+      <c r="E642" t="inlineStr"/>
+      <c r="F642" t="inlineStr"/>
+      <c r="G642" t="inlineStr"/>
+      <c r="H642" t="inlineStr"/>
+      <c r="I642" t="inlineStr"/>
+      <c r="J642" t="inlineStr"/>
       <c r="K642" t="inlineStr"/>
       <c r="L642" t="inlineStr"/>
       <c r="M642" t="inlineStr"/>
@@ -21141,7 +21141,7 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C653" t="inlineStr"/>
       <c r="D653" t="inlineStr">
@@ -21173,7 +21173,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>hrab</t>
+          <t>hreb</t>
         </is>
       </c>
       <c r="B654" t="inlineStr"/>
@@ -21190,7 +21190,7 @@
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
@@ -21233,7 +21233,7 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C656" t="inlineStr"/>
       <c r="D656" t="inlineStr">
@@ -21246,12 +21246,12 @@
           <t>ر</t>
         </is>
       </c>
-      <c r="F656" t="inlineStr"/>
-      <c r="G656" t="inlineStr">
+      <c r="F656" t="inlineStr">
         <is>
           <t>ب</t>
         </is>
       </c>
+      <c r="G656" t="inlineStr"/>
       <c r="H656" t="inlineStr"/>
       <c r="I656" t="inlineStr"/>
       <c r="J656" t="inlineStr"/>
@@ -21265,7 +21265,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>hreb</t>
+          <t xml:space="preserve">hrb </t>
         </is>
       </c>
       <c r="B657" t="inlineStr"/>
@@ -21282,14 +21282,10 @@
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="G657" t="inlineStr">
-        <is>
           <t>b</t>
         </is>
       </c>
+      <c r="G657" t="inlineStr"/>
       <c r="H657" t="inlineStr"/>
       <c r="I657" t="inlineStr"/>
       <c r="J657" t="inlineStr"/>
@@ -21325,7 +21321,7 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C659" t="inlineStr"/>
       <c r="D659" t="inlineStr">
@@ -21338,12 +21334,12 @@
           <t>ر</t>
         </is>
       </c>
-      <c r="F659" t="inlineStr">
+      <c r="F659" t="inlineStr"/>
+      <c r="G659" t="inlineStr">
         <is>
           <t>ب</t>
         </is>
       </c>
-      <c r="G659" t="inlineStr"/>
       <c r="H659" t="inlineStr"/>
       <c r="I659" t="inlineStr"/>
       <c r="J659" t="inlineStr"/>
@@ -21357,7 +21353,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t xml:space="preserve">hrb </t>
+          <t>hrab</t>
         </is>
       </c>
       <c r="B660" t="inlineStr"/>
@@ -21374,10 +21370,14 @@
       </c>
       <c r="F660" t="inlineStr">
         <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
           <t>b</t>
         </is>
       </c>
-      <c r="G660" t="inlineStr"/>
       <c r="H660" t="inlineStr"/>
       <c r="I660" t="inlineStr"/>
       <c r="J660" t="inlineStr"/>
@@ -22053,7 +22053,7 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr">
@@ -22089,14 +22089,14 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>hadiya</t>
+          <t>8adiya</t>
         </is>
       </c>
       <c r="B684" t="inlineStr"/>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
@@ -22157,7 +22157,7 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr">
@@ -22193,14 +22193,14 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>8adiya</t>
+          <t>hadiya</t>
         </is>
       </c>
       <c r="B687" t="inlineStr"/>
       <c r="C687" t="inlineStr"/>
       <c r="D687" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>h</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
@@ -22600,39 +22600,119 @@
         <v>1</v>
       </c>
       <c r="C701" t="inlineStr"/>
-      <c r="D701" t="inlineStr"/>
-      <c r="E701" t="inlineStr"/>
-      <c r="F701" t="inlineStr"/>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>ه</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>د</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>ي</t>
+        </is>
+      </c>
       <c r="G701" t="inlineStr"/>
-      <c r="H701" t="inlineStr"/>
-      <c r="I701" t="inlineStr"/>
-      <c r="J701" t="inlineStr"/>
-      <c r="K701" t="inlineStr"/>
-      <c r="L701" t="inlineStr"/>
-      <c r="M701" t="inlineStr"/>
-      <c r="N701" t="inlineStr"/>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>ة</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>ع</t>
+        </is>
+      </c>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>ي</t>
+        </is>
+      </c>
+      <c r="N701" t="inlineStr">
+        <is>
+          <t>د</t>
+        </is>
+      </c>
       <c r="O701" t="inlineStr"/>
       <c r="P701" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>هدية العيد</t>
+          <t>hdiyt l3id</t>
         </is>
       </c>
       <c r="B702" t="inlineStr"/>
       <c r="C702" t="inlineStr"/>
-      <c r="D702" t="inlineStr"/>
-      <c r="E702" t="inlineStr"/>
-      <c r="F702" t="inlineStr"/>
-      <c r="G702" t="inlineStr"/>
-      <c r="H702" t="inlineStr"/>
-      <c r="I702" t="inlineStr"/>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="J702" t="inlineStr"/>
-      <c r="K702" t="inlineStr"/>
-      <c r="L702" t="inlineStr"/>
-      <c r="M702" t="inlineStr"/>
-      <c r="N702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="N702" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
       <c r="O702" t="inlineStr"/>
       <c r="P702" t="inlineStr"/>
     </row>
@@ -22664,56 +22744,16 @@
         <v>1</v>
       </c>
       <c r="C704" t="inlineStr"/>
-      <c r="D704" t="inlineStr">
-        <is>
-          <t>ه</t>
-        </is>
-      </c>
-      <c r="E704" t="inlineStr">
-        <is>
-          <t>د</t>
-        </is>
-      </c>
-      <c r="F704" t="inlineStr">
-        <is>
-          <t>ي</t>
-        </is>
-      </c>
-      <c r="G704" t="inlineStr">
-        <is>
-          <t>ة</t>
-        </is>
-      </c>
-      <c r="H704" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="I704" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="J704" t="inlineStr">
-        <is>
-          <t>ل</t>
-        </is>
-      </c>
-      <c r="K704" t="inlineStr">
-        <is>
-          <t>ع</t>
-        </is>
-      </c>
-      <c r="L704" t="inlineStr">
-        <is>
-          <t>ي</t>
-        </is>
-      </c>
-      <c r="M704" t="inlineStr">
-        <is>
-          <t>د</t>
-        </is>
-      </c>
+      <c r="D704" t="inlineStr"/>
+      <c r="E704" t="inlineStr"/>
+      <c r="F704" t="inlineStr"/>
+      <c r="G704" t="inlineStr"/>
+      <c r="H704" t="inlineStr"/>
+      <c r="I704" t="inlineStr"/>
+      <c r="J704" t="inlineStr"/>
+      <c r="K704" t="inlineStr"/>
+      <c r="L704" t="inlineStr"/>
+      <c r="M704" t="inlineStr"/>
       <c r="N704" t="inlineStr"/>
       <c r="O704" t="inlineStr"/>
       <c r="P704" t="inlineStr"/>
@@ -22721,57 +22761,21 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>hdiat l3id</t>
+          <t>هدية العيد</t>
         </is>
       </c>
       <c r="B705" t="inlineStr"/>
       <c r="C705" t="inlineStr"/>
-      <c r="D705" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="E705" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="F705" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="G705" t="inlineStr">
-        <is>
-          <t>at</t>
-        </is>
-      </c>
-      <c r="H705" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D705" t="inlineStr"/>
+      <c r="E705" t="inlineStr"/>
+      <c r="F705" t="inlineStr"/>
+      <c r="G705" t="inlineStr"/>
+      <c r="H705" t="inlineStr"/>
       <c r="I705" t="inlineStr"/>
-      <c r="J705" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="K705" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="L705" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="M705" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
+      <c r="J705" t="inlineStr"/>
+      <c r="K705" t="inlineStr"/>
+      <c r="L705" t="inlineStr"/>
+      <c r="M705" t="inlineStr"/>
       <c r="N705" t="inlineStr"/>
       <c r="O705" t="inlineStr"/>
       <c r="P705" t="inlineStr"/>
@@ -22819,49 +22823,49 @@
           <t>ي</t>
         </is>
       </c>
-      <c r="G707" t="inlineStr"/>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>ة</t>
+        </is>
+      </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>ة</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
         <is>
-          <t> </t>
+          <t>ا</t>
         </is>
       </c>
       <c r="J707" t="inlineStr">
         <is>
-          <t>ا</t>
+          <t>ل</t>
         </is>
       </c>
       <c r="K707" t="inlineStr">
         <is>
-          <t>ل</t>
+          <t>ع</t>
         </is>
       </c>
       <c r="L707" t="inlineStr">
         <is>
-          <t>ع</t>
+          <t>ي</t>
         </is>
       </c>
       <c r="M707" t="inlineStr">
         <is>
-          <t>ي</t>
-        </is>
-      </c>
-      <c r="N707" t="inlineStr">
-        <is>
           <t>د</t>
         </is>
       </c>
+      <c r="N707" t="inlineStr"/>
       <c r="O707" t="inlineStr"/>
       <c r="P707" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>hdiyt l3id</t>
+          <t>hdiat l3id</t>
         </is>
       </c>
       <c r="B708" t="inlineStr"/>
@@ -22883,40 +22887,36 @@
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>at</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="I708" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J708" t="inlineStr"/>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr"/>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
       <c r="K708" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L708" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>i</t>
         </is>
       </c>
       <c r="M708" t="inlineStr">
         <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="N708" t="inlineStr">
-        <is>
           <t>d</t>
         </is>
       </c>
+      <c r="N708" t="inlineStr"/>
       <c r="O708" t="inlineStr"/>
       <c r="P708" t="inlineStr"/>
     </row>
@@ -22971,7 +22971,7 @@
       </c>
       <c r="I710" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J710" t="inlineStr">
@@ -23037,7 +23037,7 @@
       </c>
       <c r="I711" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J711" t="inlineStr"/>
@@ -23116,7 +23116,7 @@
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K713" t="inlineStr">
@@ -23186,7 +23186,7 @@
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K714" t="inlineStr"/>
@@ -23237,43 +23237,127 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C716" t="inlineStr"/>
-      <c r="D716" t="inlineStr"/>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>ه</t>
+        </is>
+      </c>
       <c r="E716" t="inlineStr"/>
-      <c r="F716" t="inlineStr"/>
-      <c r="G716" t="inlineStr"/>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>د</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>ي</t>
+        </is>
+      </c>
       <c r="H716" t="inlineStr"/>
-      <c r="I716" t="inlineStr"/>
-      <c r="J716" t="inlineStr"/>
-      <c r="K716" t="inlineStr"/>
-      <c r="L716" t="inlineStr"/>
-      <c r="M716" t="inlineStr"/>
-      <c r="N716" t="inlineStr"/>
-      <c r="O716" t="inlineStr"/>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>ة</t>
+        </is>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>ع</t>
+        </is>
+      </c>
+      <c r="N716" t="inlineStr">
+        <is>
+          <t>ي</t>
+        </is>
+      </c>
+      <c r="O716" t="inlineStr">
+        <is>
+          <t>د</t>
+        </is>
+      </c>
       <c r="P716" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>cadeau d l3id</t>
+          <t>hadiyat l3eid</t>
         </is>
       </c>
       <c r="B717" t="inlineStr"/>
       <c r="C717" t="inlineStr"/>
-      <c r="D717" t="inlineStr"/>
-      <c r="E717" t="inlineStr"/>
-      <c r="F717" t="inlineStr"/>
-      <c r="G717" t="inlineStr"/>
-      <c r="H717" t="inlineStr"/>
-      <c r="I717" t="inlineStr"/>
-      <c r="J717" t="inlineStr"/>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="K717" t="inlineStr"/>
-      <c r="L717" t="inlineStr"/>
-      <c r="M717" t="inlineStr"/>
-      <c r="N717" t="inlineStr"/>
-      <c r="O717" t="inlineStr"/>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N717" t="inlineStr">
+        <is>
+          <t>ei</t>
+        </is>
+      </c>
+      <c r="O717" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
       <c r="P717" t="inlineStr"/>
     </row>
     <row r="718">
@@ -23368,124 +23452,40 @@
         <v>1</v>
       </c>
       <c r="C722" t="inlineStr"/>
-      <c r="D722" t="inlineStr">
-        <is>
-          <t>ه</t>
-        </is>
-      </c>
+      <c r="D722" t="inlineStr"/>
       <c r="E722" t="inlineStr"/>
-      <c r="F722" t="inlineStr">
-        <is>
-          <t>د</t>
-        </is>
-      </c>
-      <c r="G722" t="inlineStr">
-        <is>
-          <t>ي</t>
-        </is>
-      </c>
+      <c r="F722" t="inlineStr"/>
+      <c r="G722" t="inlineStr"/>
       <c r="H722" t="inlineStr"/>
-      <c r="I722" t="inlineStr">
-        <is>
-          <t>ة</t>
-        </is>
-      </c>
-      <c r="J722" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="K722" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="L722" t="inlineStr">
-        <is>
-          <t>ل</t>
-        </is>
-      </c>
-      <c r="M722" t="inlineStr">
-        <is>
-          <t>ع</t>
-        </is>
-      </c>
-      <c r="N722" t="inlineStr">
-        <is>
-          <t>ي</t>
-        </is>
-      </c>
-      <c r="O722" t="inlineStr">
-        <is>
-          <t>د</t>
-        </is>
-      </c>
+      <c r="I722" t="inlineStr"/>
+      <c r="J722" t="inlineStr"/>
+      <c r="K722" t="inlineStr"/>
+      <c r="L722" t="inlineStr"/>
+      <c r="M722" t="inlineStr"/>
+      <c r="N722" t="inlineStr"/>
+      <c r="O722" t="inlineStr"/>
       <c r="P722" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>hadiyat l3eid</t>
+          <t>cadeau dl 3id</t>
         </is>
       </c>
       <c r="B723" t="inlineStr"/>
       <c r="C723" t="inlineStr"/>
-      <c r="D723" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="E723" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F723" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="G723" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="H723" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="I723" t="inlineStr">
-        <is>
-          <t>at</t>
-        </is>
-      </c>
-      <c r="J723" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D723" t="inlineStr"/>
+      <c r="E723" t="inlineStr"/>
+      <c r="F723" t="inlineStr"/>
+      <c r="G723" t="inlineStr"/>
+      <c r="H723" t="inlineStr"/>
+      <c r="I723" t="inlineStr"/>
+      <c r="J723" t="inlineStr"/>
       <c r="K723" t="inlineStr"/>
-      <c r="L723" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="M723" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N723" t="inlineStr">
-        <is>
-          <t>ei</t>
-        </is>
-      </c>
-      <c r="O723" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
+      <c r="L723" t="inlineStr"/>
+      <c r="M723" t="inlineStr"/>
+      <c r="N723" t="inlineStr"/>
+      <c r="O723" t="inlineStr"/>
       <c r="P723" t="inlineStr"/>
     </row>
     <row r="724">
@@ -23513,7 +23513,7 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C725" t="inlineStr"/>
       <c r="D725" t="inlineStr"/>
@@ -23533,7 +23533,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>cadeau dl 3id</t>
+          <t>cadeau d l3id</t>
         </is>
       </c>
       <c r="B726" t="inlineStr"/>
@@ -23604,7 +23604,7 @@
       </c>
       <c r="J728" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K728" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="J729" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K729" t="inlineStr">
@@ -23689,7 +23689,7 @@
       </c>
       <c r="M729" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="N729" t="inlineStr">
@@ -23760,7 +23760,7 @@
       </c>
       <c r="J731" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K731" t="inlineStr">
@@ -23830,7 +23830,7 @@
       </c>
       <c r="J732" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K732" t="inlineStr">
@@ -24141,14 +24141,34 @@
         </is>
       </c>
       <c r="B746" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C746" t="inlineStr"/>
-      <c r="D746" t="inlineStr"/>
-      <c r="E746" t="inlineStr"/>
-      <c r="F746" t="inlineStr"/>
-      <c r="G746" t="inlineStr"/>
-      <c r="H746" t="inlineStr"/>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>و</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>ن</t>
+        </is>
+      </c>
       <c r="I746" t="inlineStr"/>
       <c r="J746" t="inlineStr"/>
       <c r="K746" t="inlineStr"/>
@@ -24161,16 +24181,36 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>ألوان</t>
+          <t>alwan</t>
         </is>
       </c>
       <c r="B747" t="inlineStr"/>
       <c r="C747" t="inlineStr"/>
-      <c r="D747" t="inlineStr"/>
-      <c r="E747" t="inlineStr"/>
-      <c r="F747" t="inlineStr"/>
-      <c r="G747" t="inlineStr"/>
-      <c r="H747" t="inlineStr"/>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
       <c r="I747" t="inlineStr"/>
       <c r="J747" t="inlineStr"/>
       <c r="K747" t="inlineStr"/>
@@ -24205,34 +24245,14 @@
         </is>
       </c>
       <c r="B749" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C749" t="inlineStr"/>
-      <c r="D749" t="inlineStr">
-        <is>
-          <t>أ</t>
-        </is>
-      </c>
-      <c r="E749" t="inlineStr">
-        <is>
-          <t>ل</t>
-        </is>
-      </c>
-      <c r="F749" t="inlineStr">
-        <is>
-          <t>و</t>
-        </is>
-      </c>
-      <c r="G749" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="H749" t="inlineStr">
-        <is>
-          <t>ن</t>
-        </is>
-      </c>
+      <c r="D749" t="inlineStr"/>
+      <c r="E749" t="inlineStr"/>
+      <c r="F749" t="inlineStr"/>
+      <c r="G749" t="inlineStr"/>
+      <c r="H749" t="inlineStr"/>
       <c r="I749" t="inlineStr"/>
       <c r="J749" t="inlineStr"/>
       <c r="K749" t="inlineStr"/>
@@ -24245,36 +24265,16 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>alwan</t>
+          <t>ألوان</t>
         </is>
       </c>
       <c r="B750" t="inlineStr"/>
       <c r="C750" t="inlineStr"/>
-      <c r="D750" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="E750" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="F750" t="inlineStr">
-        <is>
-          <t>w</t>
-        </is>
-      </c>
-      <c r="G750" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="H750" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
+      <c r="D750" t="inlineStr"/>
+      <c r="E750" t="inlineStr"/>
+      <c r="F750" t="inlineStr"/>
+      <c r="G750" t="inlineStr"/>
+      <c r="H750" t="inlineStr"/>
       <c r="I750" t="inlineStr"/>
       <c r="J750" t="inlineStr"/>
       <c r="K750" t="inlineStr"/>
@@ -24589,24 +24589,12 @@
         </is>
       </c>
       <c r="B761" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C761" t="inlineStr"/>
-      <c r="D761" t="inlineStr">
-        <is>
-          <t>ر</t>
-        </is>
-      </c>
-      <c r="E761" t="inlineStr">
-        <is>
-          <t>و</t>
-        </is>
-      </c>
-      <c r="F761" t="inlineStr">
-        <is>
-          <t>ز</t>
-        </is>
-      </c>
+      <c r="D761" t="inlineStr"/>
+      <c r="E761" t="inlineStr"/>
+      <c r="F761" t="inlineStr"/>
       <c r="G761" t="inlineStr"/>
       <c r="H761" t="inlineStr"/>
       <c r="I761" t="inlineStr"/>
@@ -24621,26 +24609,14 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>roz</t>
+          <t>روز</t>
         </is>
       </c>
       <c r="B762" t="inlineStr"/>
       <c r="C762" t="inlineStr"/>
-      <c r="D762" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="E762" t="inlineStr">
-        <is>
-          <t>o</t>
-        </is>
-      </c>
-      <c r="F762" t="inlineStr">
-        <is>
-          <t>z</t>
-        </is>
-      </c>
+      <c r="D762" t="inlineStr"/>
+      <c r="E762" t="inlineStr"/>
+      <c r="F762" t="inlineStr"/>
       <c r="G762" t="inlineStr"/>
       <c r="H762" t="inlineStr"/>
       <c r="I762" t="inlineStr"/>
@@ -24677,12 +24653,24 @@
         </is>
       </c>
       <c r="B764" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C764" t="inlineStr"/>
-      <c r="D764" t="inlineStr"/>
-      <c r="E764" t="inlineStr"/>
-      <c r="F764" t="inlineStr"/>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>ر</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>و</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>ز</t>
+        </is>
+      </c>
       <c r="G764" t="inlineStr"/>
       <c r="H764" t="inlineStr"/>
       <c r="I764" t="inlineStr"/>
@@ -24697,14 +24685,26 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>روز</t>
+          <t>roz</t>
         </is>
       </c>
       <c r="B765" t="inlineStr"/>
       <c r="C765" t="inlineStr"/>
-      <c r="D765" t="inlineStr"/>
-      <c r="E765" t="inlineStr"/>
-      <c r="F765" t="inlineStr"/>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>z</t>
+        </is>
+      </c>
       <c r="G765" t="inlineStr"/>
       <c r="H765" t="inlineStr"/>
       <c r="I765" t="inlineStr"/>
@@ -24741,7 +24741,7 @@
         </is>
       </c>
       <c r="B767" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C767" t="inlineStr"/>
       <c r="D767" t="inlineStr">
@@ -24773,19 +24773,19 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>rroz</t>
+          <t>rouz</t>
         </is>
       </c>
       <c r="B768" t="inlineStr"/>
       <c r="C768" t="inlineStr"/>
       <c r="D768" t="inlineStr">
         <is>
-          <t>rr</t>
+          <t>r</t>
         </is>
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>ou</t>
         </is>
       </c>
       <c r="F768" t="inlineStr">
@@ -24829,7 +24829,7 @@
         </is>
       </c>
       <c r="B770" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C770" t="inlineStr"/>
       <c r="D770" t="inlineStr">
@@ -24861,19 +24861,19 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>rouz</t>
+          <t>rroz</t>
         </is>
       </c>
       <c r="B771" t="inlineStr"/>
       <c r="C771" t="inlineStr"/>
       <c r="D771" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>rr</t>
         </is>
       </c>
       <c r="E771" t="inlineStr">
         <is>
-          <t>ou</t>
+          <t>o</t>
         </is>
       </c>
       <c r="F771" t="inlineStr">
@@ -25845,16 +25845,12 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>ycharbo</t>
+          <t>charbou</t>
         </is>
       </c>
       <c r="B801" t="inlineStr"/>
       <c r="C801" t="inlineStr"/>
-      <c r="D801" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="D801" t="inlineStr"/>
       <c r="E801" t="inlineStr">
         <is>
           <t>ch</t>
@@ -25877,7 +25873,7 @@
       </c>
       <c r="I801" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>ou</t>
         </is>
       </c>
       <c r="J801" t="inlineStr"/>
@@ -25953,14 +25949,14 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>yachrbo</t>
+          <t>ychrbou</t>
         </is>
       </c>
       <c r="B804" t="inlineStr"/>
       <c r="C804" t="inlineStr"/>
       <c r="D804" t="inlineStr">
         <is>
-          <t>ya</t>
+          <t>y</t>
         </is>
       </c>
       <c r="E804" t="inlineStr">
@@ -25980,7 +25976,7 @@
       </c>
       <c r="H804" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>ou</t>
         </is>
       </c>
       <c r="I804" t="inlineStr"/>
@@ -26030,22 +26026,22 @@
           <t>ش</t>
         </is>
       </c>
-      <c r="F806" t="inlineStr">
+      <c r="F806" t="inlineStr"/>
+      <c r="G806" t="inlineStr">
         <is>
           <t>ر</t>
         </is>
       </c>
-      <c r="G806" t="inlineStr">
+      <c r="H806" t="inlineStr">
         <is>
           <t>ب</t>
         </is>
       </c>
-      <c r="H806" t="inlineStr">
+      <c r="I806" t="inlineStr">
         <is>
           <t>و</t>
         </is>
       </c>
-      <c r="I806" t="inlineStr"/>
       <c r="J806" t="inlineStr"/>
       <c r="K806" t="inlineStr"/>
       <c r="L806" t="inlineStr"/>
@@ -26057,7 +26053,7 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>ychrbou</t>
+          <t>ycharbo</t>
         </is>
       </c>
       <c r="B807" t="inlineStr"/>
@@ -26074,20 +26070,24 @@
       </c>
       <c r="F807" t="inlineStr">
         <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
           <t>r</t>
         </is>
       </c>
-      <c r="G807" t="inlineStr">
+      <c r="H807" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="H807" t="inlineStr">
-        <is>
-          <t>ou</t>
-        </is>
-      </c>
-      <c r="I807" t="inlineStr"/>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
       <c r="J807" t="inlineStr"/>
       <c r="K807" t="inlineStr"/>
       <c r="L807" t="inlineStr"/>
@@ -26121,7 +26121,7 @@
         </is>
       </c>
       <c r="B809" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C809" t="inlineStr"/>
       <c r="D809" t="inlineStr">
@@ -26161,12 +26161,16 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>charbou</t>
+          <t>ycherbo</t>
         </is>
       </c>
       <c r="B810" t="inlineStr"/>
       <c r="C810" t="inlineStr"/>
-      <c r="D810" t="inlineStr"/>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E810" t="inlineStr">
         <is>
           <t>ch</t>
@@ -26174,7 +26178,7 @@
       </c>
       <c r="F810" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="G810" t="inlineStr">
@@ -26189,7 +26193,7 @@
       </c>
       <c r="I810" t="inlineStr">
         <is>
-          <t>ou</t>
+          <t>o</t>
         </is>
       </c>
       <c r="J810" t="inlineStr"/>
@@ -26225,7 +26229,7 @@
         </is>
       </c>
       <c r="B812" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C812" t="inlineStr"/>
       <c r="D812" t="inlineStr">
@@ -26238,22 +26242,22 @@
           <t>ش</t>
         </is>
       </c>
-      <c r="F812" t="inlineStr"/>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>ر</t>
+        </is>
+      </c>
       <c r="G812" t="inlineStr">
         <is>
-          <t>ر</t>
+          <t>ب</t>
         </is>
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>ب</t>
-        </is>
-      </c>
-      <c r="I812" t="inlineStr">
-        <is>
           <t>و</t>
         </is>
       </c>
+      <c r="I812" t="inlineStr"/>
       <c r="J812" t="inlineStr"/>
       <c r="K812" t="inlineStr"/>
       <c r="L812" t="inlineStr"/>
@@ -26265,14 +26269,14 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>ycherbo</t>
+          <t>yachrbo</t>
         </is>
       </c>
       <c r="B813" t="inlineStr"/>
       <c r="C813" t="inlineStr"/>
       <c r="D813" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>ya</t>
         </is>
       </c>
       <c r="E813" t="inlineStr">
@@ -26282,24 +26286,20 @@
       </c>
       <c r="F813" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>r</t>
         </is>
       </c>
       <c r="G813" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>b</t>
         </is>
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="I813" t="inlineStr">
-        <is>
           <t>o</t>
         </is>
       </c>
+      <c r="I813" t="inlineStr"/>
       <c r="J813" t="inlineStr"/>
       <c r="K813" t="inlineStr"/>
       <c r="L813" t="inlineStr"/>
@@ -26333,35 +26333,15 @@
         </is>
       </c>
       <c r="B815" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C815" t="inlineStr"/>
-      <c r="D815" t="inlineStr">
-        <is>
-          <t>ي</t>
-        </is>
-      </c>
-      <c r="E815" t="inlineStr">
-        <is>
-          <t>ش</t>
-        </is>
-      </c>
+      <c r="D815" t="inlineStr"/>
+      <c r="E815" t="inlineStr"/>
       <c r="F815" t="inlineStr"/>
-      <c r="G815" t="inlineStr">
-        <is>
-          <t>ر</t>
-        </is>
-      </c>
-      <c r="H815" t="inlineStr">
-        <is>
-          <t>ب</t>
-        </is>
-      </c>
-      <c r="I815" t="inlineStr">
-        <is>
-          <t>و</t>
-        </is>
-      </c>
+      <c r="G815" t="inlineStr"/>
+      <c r="H815" t="inlineStr"/>
+      <c r="I815" t="inlineStr"/>
       <c r="J815" t="inlineStr"/>
       <c r="K815" t="inlineStr"/>
       <c r="L815" t="inlineStr"/>
@@ -26373,41 +26353,17 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>icherbou</t>
+          <t>kicherbo</t>
         </is>
       </c>
       <c r="B816" t="inlineStr"/>
       <c r="C816" t="inlineStr"/>
-      <c r="D816" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="E816" t="inlineStr">
-        <is>
-          <t>ch</t>
-        </is>
-      </c>
-      <c r="F816" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="G816" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="H816" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="I816" t="inlineStr">
-        <is>
-          <t>ou</t>
-        </is>
-      </c>
+      <c r="D816" t="inlineStr"/>
+      <c r="E816" t="inlineStr"/>
+      <c r="F816" t="inlineStr"/>
+      <c r="G816" t="inlineStr"/>
+      <c r="H816" t="inlineStr"/>
+      <c r="I816" t="inlineStr"/>
       <c r="J816" t="inlineStr"/>
       <c r="K816" t="inlineStr"/>
       <c r="L816" t="inlineStr"/>
@@ -26441,15 +26397,35 @@
         </is>
       </c>
       <c r="B818" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C818" t="inlineStr"/>
-      <c r="D818" t="inlineStr"/>
-      <c r="E818" t="inlineStr"/>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>ي</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>ش</t>
+        </is>
+      </c>
       <c r="F818" t="inlineStr"/>
-      <c r="G818" t="inlineStr"/>
-      <c r="H818" t="inlineStr"/>
-      <c r="I818" t="inlineStr"/>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>ر</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>و</t>
+        </is>
+      </c>
       <c r="J818" t="inlineStr"/>
       <c r="K818" t="inlineStr"/>
       <c r="L818" t="inlineStr"/>
@@ -26461,17 +26437,41 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>kicherbo</t>
+          <t>ycherbou</t>
         </is>
       </c>
       <c r="B819" t="inlineStr"/>
       <c r="C819" t="inlineStr"/>
-      <c r="D819" t="inlineStr"/>
-      <c r="E819" t="inlineStr"/>
-      <c r="F819" t="inlineStr"/>
-      <c r="G819" t="inlineStr"/>
-      <c r="H819" t="inlineStr"/>
-      <c r="I819" t="inlineStr"/>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>ou</t>
+        </is>
+      </c>
       <c r="J819" t="inlineStr"/>
       <c r="K819" t="inlineStr"/>
       <c r="L819" t="inlineStr"/>
@@ -26505,7 +26505,7 @@
         </is>
       </c>
       <c r="B821" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C821" t="inlineStr"/>
       <c r="D821" t="inlineStr">
@@ -26545,14 +26545,14 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>ycherbou</t>
+          <t>icherbou</t>
         </is>
       </c>
       <c r="B822" t="inlineStr"/>
       <c r="C822" t="inlineStr"/>
       <c r="D822" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
       <c r="E822" t="inlineStr">
@@ -26616,32 +26616,12 @@
         <v>1</v>
       </c>
       <c r="C824" t="inlineStr"/>
-      <c r="D824" t="inlineStr">
-        <is>
-          <t>ي</t>
-        </is>
-      </c>
-      <c r="E824" t="inlineStr">
-        <is>
-          <t>ش</t>
-        </is>
-      </c>
-      <c r="F824" t="inlineStr">
-        <is>
-          <t>ر</t>
-        </is>
-      </c>
+      <c r="D824" t="inlineStr"/>
+      <c r="E824" t="inlineStr"/>
+      <c r="F824" t="inlineStr"/>
       <c r="G824" t="inlineStr"/>
-      <c r="H824" t="inlineStr">
-        <is>
-          <t>ب</t>
-        </is>
-      </c>
-      <c r="I824" t="inlineStr">
-        <is>
-          <t>و</t>
-        </is>
-      </c>
+      <c r="H824" t="inlineStr"/>
+      <c r="I824" t="inlineStr"/>
       <c r="J824" t="inlineStr"/>
       <c r="K824" t="inlineStr"/>
       <c r="L824" t="inlineStr"/>
@@ -26653,41 +26633,17 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>yachribou</t>
+          <t>kaycherbu</t>
         </is>
       </c>
       <c r="B825" t="inlineStr"/>
       <c r="C825" t="inlineStr"/>
-      <c r="D825" t="inlineStr">
-        <is>
-          <t>ya</t>
-        </is>
-      </c>
-      <c r="E825" t="inlineStr">
-        <is>
-          <t>ch</t>
-        </is>
-      </c>
-      <c r="F825" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="G825" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="H825" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="I825" t="inlineStr">
-        <is>
-          <t>ou</t>
-        </is>
-      </c>
+      <c r="D825" t="inlineStr"/>
+      <c r="E825" t="inlineStr"/>
+      <c r="F825" t="inlineStr"/>
+      <c r="G825" t="inlineStr"/>
+      <c r="H825" t="inlineStr"/>
+      <c r="I825" t="inlineStr"/>
       <c r="J825" t="inlineStr"/>
       <c r="K825" t="inlineStr"/>
       <c r="L825" t="inlineStr"/>
@@ -26793,28 +26749,28 @@
           <t>ي</t>
         </is>
       </c>
-      <c r="E830" t="inlineStr"/>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>ش</t>
+        </is>
+      </c>
       <c r="F830" t="inlineStr">
         <is>
-          <t>ش</t>
+          <t>ر</t>
         </is>
       </c>
       <c r="G830" t="inlineStr"/>
       <c r="H830" t="inlineStr">
         <is>
-          <t>ر</t>
+          <t>ب</t>
         </is>
       </c>
       <c r="I830" t="inlineStr">
         <is>
-          <t>ب</t>
-        </is>
-      </c>
-      <c r="J830" t="inlineStr">
-        <is>
           <t>و</t>
         </is>
       </c>
+      <c r="J830" t="inlineStr"/>
       <c r="K830" t="inlineStr"/>
       <c r="L830" t="inlineStr"/>
       <c r="M830" t="inlineStr"/>
@@ -26825,46 +26781,42 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>yoshorbou</t>
+          <t>yachribou</t>
         </is>
       </c>
       <c r="B831" t="inlineStr"/>
       <c r="C831" t="inlineStr"/>
       <c r="D831" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>ya</t>
         </is>
       </c>
       <c r="E831" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>ch</t>
         </is>
       </c>
       <c r="F831" t="inlineStr">
         <is>
-          <t>sh</t>
+          <t>r</t>
         </is>
       </c>
       <c r="G831" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>i</t>
         </is>
       </c>
       <c r="H831" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>b</t>
         </is>
       </c>
       <c r="I831" t="inlineStr">
         <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="J831" t="inlineStr">
-        <is>
           <t>ou</t>
         </is>
       </c>
+      <c r="J831" t="inlineStr"/>
       <c r="K831" t="inlineStr"/>
       <c r="L831" t="inlineStr"/>
       <c r="M831" t="inlineStr"/>
@@ -26900,13 +26852,33 @@
         <v>1</v>
       </c>
       <c r="C833" t="inlineStr"/>
-      <c r="D833" t="inlineStr"/>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>ي</t>
+        </is>
+      </c>
       <c r="E833" t="inlineStr"/>
-      <c r="F833" t="inlineStr"/>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>ش</t>
+        </is>
+      </c>
       <c r="G833" t="inlineStr"/>
-      <c r="H833" t="inlineStr"/>
-      <c r="I833" t="inlineStr"/>
-      <c r="J833" t="inlineStr"/>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>ر</t>
+        </is>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="J833" t="inlineStr">
+        <is>
+          <t>و</t>
+        </is>
+      </c>
       <c r="K833" t="inlineStr"/>
       <c r="L833" t="inlineStr"/>
       <c r="M833" t="inlineStr"/>
@@ -26917,18 +26889,46 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>kaycherbu</t>
+          <t>yoshorbou</t>
         </is>
       </c>
       <c r="B834" t="inlineStr"/>
       <c r="C834" t="inlineStr"/>
-      <c r="D834" t="inlineStr"/>
-      <c r="E834" t="inlineStr"/>
-      <c r="F834" t="inlineStr"/>
-      <c r="G834" t="inlineStr"/>
-      <c r="H834" t="inlineStr"/>
-      <c r="I834" t="inlineStr"/>
-      <c r="J834" t="inlineStr"/>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>sh</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>ou</t>
+        </is>
+      </c>
       <c r="K834" t="inlineStr"/>
       <c r="L834" t="inlineStr"/>
       <c r="M834" t="inlineStr"/>
@@ -27249,7 +27249,7 @@
         </is>
       </c>
       <c r="B848" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C848" t="inlineStr"/>
       <c r="D848" t="inlineStr">
@@ -27285,7 +27285,7 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>baya3</t>
+          <t>biya3</t>
         </is>
       </c>
       <c r="B849" t="inlineStr"/>
@@ -27297,7 +27297,7 @@
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>i</t>
         </is>
       </c>
       <c r="F849" t="inlineStr">
@@ -27349,7 +27349,7 @@
         </is>
       </c>
       <c r="B851" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C851" t="inlineStr"/>
       <c r="D851" t="inlineStr">
@@ -27385,7 +27385,7 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>biya3</t>
+          <t>baya3</t>
         </is>
       </c>
       <c r="B852" t="inlineStr"/>
@@ -27397,7 +27397,7 @@
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F852" t="inlineStr">
@@ -27485,7 +27485,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>beyaea</t>
+          <t>biyya3</t>
         </is>
       </c>
       <c r="B855" t="inlineStr"/>
@@ -27497,22 +27497,22 @@
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>i</t>
         </is>
       </c>
       <c r="F855" t="inlineStr">
         <is>
-          <t>ya</t>
+          <t>yy</t>
         </is>
       </c>
       <c r="G855" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H855" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I855" t="inlineStr"/>
@@ -27585,7 +27585,7 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>biyya3</t>
+          <t>beyaea</t>
         </is>
       </c>
       <c r="B858" t="inlineStr"/>
@@ -27597,22 +27597,22 @@
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F858" t="inlineStr">
         <is>
-          <t>yy</t>
+          <t>ya</t>
         </is>
       </c>
       <c r="G858" t="inlineStr">
         <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
           <t>a</t>
-        </is>
-      </c>
-      <c r="H858" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I858" t="inlineStr"/>
@@ -28561,7 +28561,7 @@
         </is>
       </c>
       <c r="B899" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C899" t="inlineStr"/>
       <c r="D899" t="inlineStr">
@@ -28605,7 +28605,7 @@
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>yasmine</t>
+          <t>yassmin</t>
         </is>
       </c>
       <c r="B900" t="inlineStr"/>
@@ -28622,7 +28622,7 @@
       </c>
       <c r="F900" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>ss</t>
         </is>
       </c>
       <c r="G900" t="inlineStr">
@@ -28640,11 +28640,7 @@
           <t>n</t>
         </is>
       </c>
-      <c r="J900" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
+      <c r="J900" t="inlineStr"/>
       <c r="K900" t="inlineStr"/>
       <c r="L900" t="inlineStr"/>
       <c r="M900" t="inlineStr"/>
@@ -28677,7 +28673,7 @@
         </is>
       </c>
       <c r="B902" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C902" t="inlineStr"/>
       <c r="D902" t="inlineStr">
@@ -28721,7 +28717,7 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>yassmin</t>
+          <t>yasmine</t>
         </is>
       </c>
       <c r="B903" t="inlineStr"/>
@@ -28738,7 +28734,7 @@
       </c>
       <c r="F903" t="inlineStr">
         <is>
-          <t>ss</t>
+          <t>s</t>
         </is>
       </c>
       <c r="G903" t="inlineStr">
@@ -28756,7 +28752,11 @@
           <t>n</t>
         </is>
       </c>
-      <c r="J903" t="inlineStr"/>
+      <c r="J903" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
       <c r="K903" t="inlineStr"/>
       <c r="L903" t="inlineStr"/>
       <c r="M903" t="inlineStr"/>
@@ -29373,7 +29373,7 @@
         </is>
       </c>
       <c r="B923" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C923" t="inlineStr"/>
       <c r="D923" t="inlineStr">
@@ -29413,7 +29413,7 @@
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>guitare</t>
+          <t>guitara</t>
         </is>
       </c>
       <c r="B924" t="inlineStr"/>
@@ -29450,7 +29450,7 @@
       </c>
       <c r="J924" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="K924" t="inlineStr"/>
@@ -29485,7 +29485,7 @@
         </is>
       </c>
       <c r="B926" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C926" t="inlineStr"/>
       <c r="D926" t="inlineStr">
@@ -29525,7 +29525,7 @@
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>guitara</t>
+          <t>guitare</t>
         </is>
       </c>
       <c r="B927" t="inlineStr"/>
@@ -29562,7 +29562,7 @@
       </c>
       <c r="J927" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="K927" t="inlineStr"/>
